--- a/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:04</t>
+          <t>2026-09-02 00:54:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:05</t>
+          <t>2026-09-02 00:54:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:06</t>
+          <t>2026-09-02 00:54:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:08</t>
+          <t>2026-09-02 00:54:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:08</t>
+          <t>2026-09-02 00:54:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:08</t>
+          <t>2026-09-02 00:54:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:08</t>
+          <t>2026-09-02 00:54:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:08</t>
+          <t>2026-09-02 00:54:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:47</t>
+          <t>2026-09-02 01:21:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:48</t>
+          <t>2026-09-02 01:21:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:49</t>
+          <t>2026-09-02 01:21:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:51</t>
+          <t>2026-09-02 01:21:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:51</t>
+          <t>2026-09-02 01:21:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:51</t>
+          <t>2026-09-02 01:21:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:51</t>
+          <t>2026-09-02 01:21:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:54:51</t>
+          <t>2026-09-02 01:21:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>-2.25%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.96%753,000</t>
+          <t>8.97%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>8.97%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.21%14150</t>
+          <t>-2.01%13865</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14150</v>
+        <v>13865</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.61%80,000</t>
+          <t>5.52%80,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>-0.93%4275</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4315</v>
+        <v>4275</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.84%249,000</t>
+          <t>5.24%249,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.97%3425</t>
+          <t>-0.88%3395</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3425</v>
+        <v>3395</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.99%228,600</t>
+          <t>3.82%228,600</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>-3.46%5445</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5640</v>
+        <v>5445</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.69%136,000</t>
+          <t>3.74%136,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1865</v>
+        <v>1730</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.6%518</t>
+          <t>0%518</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.95%1,096,000</t>
+          <t>2.77%1,096,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.3%234.5</t>
+          <t>+1.28%237.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>234.5</v>
+        <v>237.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.90%2,416,000</t>
+          <t>2.76%2,416,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+0.21%973</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.78%563,000</t>
+          <t>2.67%563,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.4%256</t>
+          <t>-1.95%251</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.38%1,921,000</t>
+          <t>2.40%1,921,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.15%1225</t>
+          <t>-4.08%1175</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.15%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1225</v>
+        <v>1175</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.27%393,000</t>
+          <t>2.35%393,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>-2.93%3310</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3410</v>
+        <v>3310</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.27%134,000</t>
+          <t>2.23%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.17%5870</t>
+          <t>-2.73%5710</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5870</v>
+        <v>5710</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.12%73,000</t>
+          <t>2.09%73,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.85%2125</t>
+          <t>-2.82%2065</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2125</v>
+        <v>2065</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.11%197,000</t>
+          <t>2.04%197,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:19</t>
+          <t>2026-09-02 16:25:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.56%176</t>
+          <t>0%2610</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>176</v>
+        <v>2610</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.07%2,293,000</t>
+          <t>1.98%52,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2293000</v>
+        <v>52000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>-1.95%5770</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5885</v>
+        <v>5770</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.05%69,000</t>
+          <t>1.98%69,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6669緯穎科技服務</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>+1.7%179</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7800</v>
+        <v>179</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.83%52,000</t>
+          <t>1.97%2,293,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>52000</v>
+        <v>2293000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-2.22%5290</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5410</v>
+        <v>5290</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.83%72,000</t>
+          <t>1.90%72,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5995</v>
+        <v>2140</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.78%59,000</t>
+          <t>1.87%174,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>59000</v>
+        <v>174000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>+2.03%7050</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2205</v>
+        <v>7050</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.75%174,000</t>
+          <t>1.85%55,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>174000</v>
+        <v>55000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6515穎崴科技</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+9.94%6910</t>
+          <t>-1.67%5895</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6910</v>
+        <v>5895</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.71%55,000</t>
+          <t>1.73%59,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>55000</v>
+        <v>59000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,25 +1785,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.03%342</t>
+          <t>-4.93%540</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-4.93%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>342</v>
+        <v>540</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.65%987,000</t>
+          <t>1.65%595,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>987000</v>
+        <v>595000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+4.22%568</t>
+          <t>-1.46%337</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>568</v>
+        <v>337</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.60%595,000</t>
+          <t>1.65%987,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>595000</v>
+        <v>987000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.52%526,000</t>
+          <t>1.57%526,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1450</v>
+        <v>17725</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.48%209,000</t>
+          <t>1.53%18,300</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>209000</v>
+        <v>18300</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>17120</v>
+        <v>1410</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.45%18,300</t>
+          <t>1.48%209,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>18300</v>
+        <v>209000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.78%66.5</t>
+          <t>-2.71%1975</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>66.5</v>
+        <v>1975</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.45%4,525,000</t>
+          <t>1.47%148,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>4525000</v>
+        <v>148000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>+0.15%66.6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2030</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.44%148,000</t>
+          <t>1.47%4,525,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>148000</v>
+        <v>4525000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.36%550</t>
+          <t>-2.55%536</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.31%482,000</t>
+          <t>1.29%482,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:20</t>
+          <t>2026-09-02 16:25:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.38%39.9</t>
+          <t>+1.5%40.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.25%6,340,622</t>
+          <t>1.23%6,340,622</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>2376技嘉科技</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>+0.7%361.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1225</v>
+        <v>361.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.24%203,000</t>
+          <t>1.22%694,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>203000</v>
+        <v>694000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2376技嘉科技</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.28%359</t>
+          <t>-2.04%1200</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>359</v>
+        <v>1200</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.23%694,000</t>
+          <t>1.21%203,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>694000</v>
+        <v>203000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5904寶雅國際</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2%73.5</t>
+          <t>-5.23%507</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>73.5</v>
+        <v>507</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.16%3,124,500</t>
+          <t>1.20%461,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>3124500</v>
+        <v>461000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4958臻鼎科技控股</t>
+          <t>5904寶雅國際</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+7%535</t>
+          <t>-0.14%73.4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>535</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.14%461,000</t>
+          <t>1.12%3,124,500</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>461000</v>
+        <v>3124500</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0%196</t>
+          <t>-4.59%187</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.11%1,147,000</t>
+          <t>1.10%1,147,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%1175</t>
+          <t>+7.66%1265</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1175</v>
+        <v>1265</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.05%181,000</t>
+          <t>1.04%181,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+3.03%7810</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7580</v>
+        <v>7810</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.98%26,000</t>
+          <t>0.96%26,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+2.17%990</t>
+          <t>-2.22%968</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.25%182</t>
+          <t>+1.92%185.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.25%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>182</v>
+        <v>185.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.6%711</t>
+          <t>-0.42%708</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.91%252,000</t>
+          <t>0.87%252,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.31%503</t>
+          <t>-0.2%502</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+6.72%874</t>
+          <t>-3.09%847</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+6.72%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>874</v>
+        <v>847</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.75%185,000</t>
+          <t>0.79%185,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.17%237.5</t>
+          <t>-1.68%233.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.17%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>237.5</v>
+        <v>233.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.73%650,000</t>
+          <t>0.75%650,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.87%2285</t>
+          <t>-7.66%2110</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-7.66%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2285</v>
+        <v>2110</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.62%54,000</t>
+          <t>0.60%54,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:21</t>
+          <t>2026-09-02 16:25:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6831邁科科技</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.46%609</t>
+          <t>-9.28%2395</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-9.28%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>609</v>
+        <v>2395</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.56%182,000</t>
+          <t>0.57%44,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>182000</v>
+        <v>44000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:23</t>
+          <t>2026-09-02 16:25:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>6831邁科科技</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+10%2640</t>
+          <t>0%609</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2640</v>
+        <v>609</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.52%44,000</t>
+          <t>0.54%182,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>44000</v>
+        <v>182000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:23</t>
+          <t>2026-09-02 16:25:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.48%731</t>
+          <t>-6.16%686</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-6.16%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>731</v>
+        <v>686</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.49%134,000</t>
+          <t>0.48%134,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:23</t>
+          <t>2026-09-02 16:25:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2315</v>
+        <v>2170</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.35%32,336</t>
+          <t>0.37%32,336</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:23</t>
+          <t>2026-09-02 16:25:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3533嘉澤端子工業</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.31%1635</t>
+          <t>-2.29%1705</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1635</v>
+        <v>1705</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.31%38,000</t>
+          <t>0.30%35,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:23</t>
+          <t>2026-09-02 16:25:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,38 +3493,38 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3533嘉澤端子工業</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+3.25%1745</t>
+          <t>+9.79%1795</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>+9.79%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1745</v>
+        <v>1795</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.29%35,000</t>
+          <t>0.30%38,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:18</t>
+          <t>2026-09-02 19:48:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:20</t>
+          <t>2026-09-02 19:48:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:21</t>
+          <t>2026-09-02 19:48:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:22</t>
+          <t>2026-09-02 19:48:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:22</t>
+          <t>2026-09-02 19:48:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:22</t>
+          <t>2026-09-02 19:48:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:22</t>
+          <t>2026-09-02 19:48:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:22</t>
+          <t>2026-09-02 19:48:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:38</t>
+          <t>2026-09-02 22:20:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:39</t>
+          <t>2026-09-02 22:20:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:41</t>
+          <t>2026-09-02 22:20:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:42</t>
+          <t>2026-09-02 22:20:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:42</t>
+          <t>2026-09-02 22:20:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:42</t>
+          <t>2026-09-02 22:20:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:42</t>
+          <t>2026-09-02 22:20:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:42</t>
+          <t>2026-09-02 22:20:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:35</t>
+          <t>2026-09-02 23:15:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:36</t>
+          <t>2026-09-02 23:15:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:37</t>
+          <t>2026-09-02 23:15:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:39</t>
+          <t>2026-09-02 23:15:56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:39</t>
+          <t>2026-09-02 23:15:56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:39</t>
+          <t>2026-09-02 23:15:56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:39</t>
+          <t>2026-09-02 23:15:56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:39</t>
+          <t>2026-09-02 23:15:56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
